--- a/training_loss_log.xlsx
+++ b/training_loss_log.xlsx
@@ -413,24 +413,1054 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Time (s)</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Average Loss</t>
+          <t>Avg Total Loss</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Batches</t>
+          <t>Avg Policy Loss</t>
         </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Avg KL Div</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Avg Grad Norm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>8.543530030231922</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8.095459297811612</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.640101056155736</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12.31687444925308</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>200</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4.73179199391976</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.940972240651027</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.129742520566797</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.871299846172333</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>300</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4.309305497542955</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.56236472570803</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.067058259915793</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.542596495151519</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>400</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4.076257843663916</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.343427635859698</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.046900317693362</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4.751726410388946</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4.071080414927565</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.344554214607924</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.037894587985356</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.720021405220032</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>600</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4.243771206103265</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.500701112258248</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.061528721417999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.719918224811554</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>700</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4.38755330234766</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.629511306276545</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.082917147381231</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.39713692188263</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>800</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4.20209086837247</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.438122673910111</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.091383152699564</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.108744525909424</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>900</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4.277910974118859</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.550470306230709</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.039200968737714</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5.234286375045777</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4.578262759223581</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.763552640080452</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.163871616158867</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.752034764289856</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4.440083491764963</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.609199595148675</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.186977013453143</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5.975108218193054</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4.345378743335605</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.5322732086014</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.161579352794215</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6.355989153385162</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1300</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4.255366096096114</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.468246198771522</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.124457013155334</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6.126497378349304</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4.355455199871212</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.514922282476909</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.200761327419896</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6.743033905029296</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B16" t="n">
+        <v>4.640779455620796</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.758497023880482</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.260403495165519</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7.115657811164856</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1600</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4.393360080569982</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.595155837833881</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.140291792950593</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6.793069906234741</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1700</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4.614285661317408</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.758405365878716</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.222686157329008</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7.038824691772461</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4.267178243510426</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.489966644477099</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.11030230238568</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6.853797516822815</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4.542118815286085</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.69806893741712</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.205785557787167</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6.891151742935181</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4.381859802929685</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.533487762026489</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.211960074708331</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6.9148663854599</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4.095571961980313</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.33073333508335</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.092626626603305</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7.14622905254364</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2200</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4.044189887372777</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.268080914029852</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.108727122902637</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7.038997373580933</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2300</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4.238399818241597</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.466605109442026</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.102563885734416</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6.900622110366822</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4.384153576213866</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.523770936578512</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.229118072611745</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7.70917142868042</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4.530895169060678</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.686302857818082</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.206560462517664</v>
+      </c>
+      <c r="E26" t="n">
+        <v>8.093351879119872</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2600</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4.151388014769181</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.374864847399294</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.109318827216048</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7.311807408332824</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2700</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4.317942972285673</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.530118767144158</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.125463168418501</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7.521268301010132</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2800</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4.303077860325575</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.470955994883552</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.188745540764649</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7.868100509643555</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2900</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4.197855905117467</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3.379331510802731</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.169320581387729</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7.476617488861084</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4.336655170815066</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.503358464566991</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.190423886207864</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7.961998596191406</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3100</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4.232720369827002</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.450126847140491</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.117990763974376</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7.737096757888794</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3200</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4.110895009506494</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.294154236651957</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.166772549939342</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7.666250386238098</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3300</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4.262623606240377</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3.43337457023561</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.184641496228287</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7.960474042892456</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3400</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4.339353771125897</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3.530285678822547</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.155811579817673</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7.538073287010193</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3500</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4.278268981520086</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3.433969963276759</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.206141469369177</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8.133077893257141</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3600</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4.276289790580049</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3.490332637066022</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.122795953138266</v>
+      </c>
+      <c r="E37" t="n">
+        <v>8.169020972251893</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3700</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4.356216319641098</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3.526761637479067</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.184935277947225</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8.674096336364746</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3800</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4.435102296415717</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3.612939712423831</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.174517993207555</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8.711169910430907</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3900</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4.407745086373762</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3.591514025283977</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.166044391503092</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8.85941586971283</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4000</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4.385988795654848</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.596938950596377</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.127214081601705</v>
+      </c>
+      <c r="E41" t="n">
+        <v>8.583044972419739</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4100</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4.27457414008677</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.4576736558415</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.167000708125997</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8.499034395217896</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4200</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4.124161579050123</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.319487194223329</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.149534852444194</v>
+      </c>
+      <c r="E43" t="n">
+        <v>8.070078921318053</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4300</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4.082860143743456</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3.229818920074031</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.21863033774076</v>
+      </c>
+      <c r="E44" t="n">
+        <v>8.287519497871399</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4400</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4.51382423507981</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.632052854504436</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.259673419031315</v>
+      </c>
+      <c r="E45" t="n">
+        <v>9.316698889732361</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4500</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4.338280482152477</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3.483334672441706</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.221351175822783</v>
+      </c>
+      <c r="E46" t="n">
+        <v>8.204313578605651</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4600</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4.351591613180935</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3.503160090278834</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.212045053064357</v>
+      </c>
+      <c r="E47" t="n">
+        <v>8.294432311058044</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4700</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4.371071436721832</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3.527503369348123</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.20509725486394</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8.693281517028808</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4800</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4.367902734903619</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3.546689069410786</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.173162395574618</v>
+      </c>
+      <c r="E49" t="n">
+        <v>8.608360204696655</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4900</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4.235113369049504</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.417541152564809</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.16796032495331</v>
+      </c>
+      <c r="E50" t="n">
+        <v>8.939480171203613</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B51" t="n">
+        <v>4.359251650497317</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3.566573573118076</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1.132397270320216</v>
+      </c>
+      <c r="E51" t="n">
+        <v>8.79189826965332</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5100</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4.118889498161152</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3.330868884231895</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.125743753442075</v>
+      </c>
+      <c r="E52" t="n">
+        <v>8.638102016448975</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>5200</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4.084562371708452</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3.297237889114767</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.124749276477378</v>
+      </c>
+      <c r="E53" t="n">
+        <v>8.3197585439682</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>5300</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4.127487025391311</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3.330194317223504</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.138989598199259</v>
+      </c>
+      <c r="E54" t="n">
+        <v>8.948091044425965</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5400</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4.313069905014709</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3.493515312932432</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.170792289061938</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9.787324733734131</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5500</v>
+      </c>
+      <c r="B56" t="n">
+        <v>4.447173446156085</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3.626896205469966</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.171824648596812</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9.866244864463805</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5600</v>
+      </c>
+      <c r="B57" t="n">
+        <v>4.161375899761915</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3.390102662099525</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.101818931458983</v>
+      </c>
+      <c r="E57" t="n">
+        <v>8.758299493789673</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>5700</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4.318357286704704</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.520282825483009</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.14010638941545</v>
+      </c>
+      <c r="E58" t="n">
+        <v>9.121594448089599</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5800</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4.500174826597795</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3.646211791783571</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.219947210329119</v>
+      </c>
+      <c r="E59" t="n">
+        <v>9.307678623199463</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>5900</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4.181197453550994</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3.439202236873098</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.059993184835184</v>
+      </c>
+      <c r="E60" t="n">
+        <v>9.216917033195495</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>6000</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4.338853129753843</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3.568632160844281</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1.100315685670357</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9.476157479286194</v>
       </c>
     </row>
   </sheetData>
